--- a/00_Administración/presupuesto_banco_ensayos.xlsx
+++ b/00_Administración/presupuesto_banco_ensayos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josei\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udeconce-my.sharepoint.com/personal/joarriagada2021_udec_cl/Documents/Escritorio/Memoria/00_Administración/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A087F001-3914-46A3-8F91-971FE9E8414F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A087F001-3914-46A3-8F91-971FE9E8414F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7785E24-2004-4893-9BB7-FDCCF43C2850}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -193,7 +193,7 @@
     <numFmt numFmtId="164" formatCode="\$#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,6 +266,14 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -317,10 +325,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -359,8 +368,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -927,7 +940,7 @@
         <f>B18*C18</f>
         <v>9082</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="20" t="s">
         <v>33</v>
       </c>
       <c r="F18" s="8" t="s">

--- a/00_Administración/presupuesto_banco_ensayos.xlsx
+++ b/00_Administración/presupuesto_banco_ensayos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://udeconce-my.sharepoint.com/personal/joarriagada2021_udec_cl/Documents/Escritorio/Memoria/00_Administración/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A087F001-3914-46A3-8F91-971FE9E8414F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7785E24-2004-4893-9BB7-FDCCF43C2850}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{A087F001-3914-46A3-8F91-971FE9E8414F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84DD10A2-98F6-4A30-9313-01F3C420AC9C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Presupuesto consolidado — banco de ensayos (Memoria de Título)</t>
   </si>
@@ -183,17 +183,21 @@
   </si>
   <si>
     <t>Reductor de voltaje DC-DC ajustable (4–36 V a 1,25–36 V, máx. 8 A / 200 W). Baja los 12 V de la fuente a 6 V</t>
+  </si>
+  <si>
+    <t>Impuestos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="42" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="\$#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,6 +278,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -325,11 +336,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -358,12 +370,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -371,9 +381,14 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Moneda [0]" xfId="2" builtinId="7"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -940,7 +955,7 @@
         <f>B18*C18</f>
         <v>9082</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="18" t="s">
         <v>33</v>
       </c>
       <c r="F18" s="8" t="s">
@@ -988,7 +1003,7 @@
       <c r="C21" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="22">
         <f>SUM(D6:D19)</f>
         <v>115275</v>
       </c>
@@ -998,7 +1013,7 @@
       <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="17" t="s">
         <v>41</v>
       </c>
       <c r="D22">
@@ -1008,10 +1023,10 @@
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="15">
         <v>0.1</v>
       </c>
       <c r="E23" s="3"/>
@@ -1022,10 +1037,10 @@
     <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="21">
         <f>D21*D23</f>
         <v>11527.5</v>
       </c>
@@ -1037,12 +1052,11 @@
     <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
-      <c r="C25" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="18">
-        <f>D21+D24+D22</f>
-        <v>154222.5</v>
+      <c r="C25" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="20">
+        <v>22460</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1052,8 +1066,13 @@
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
+      <c r="C26" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="16">
+        <f>D21+D24+D22+D25</f>
+        <v>176682.5</v>
+      </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -1074,7 +1093,7 @@
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
+      <c r="E28" s="19"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
